--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Game.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Game.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5319" uniqueCount="4114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5334" uniqueCount="4123">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -11099,6 +11099,21 @@
     <t xml:space="preserve">バックパックの中にベッドが見つからない。アビリティの「休憩」を使えば睡眠は取れるが…</t>
   </si>
   <si>
+    <t xml:space="preserve">noBinoFound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">백팩 속에 쌍안경이 보이지 않는다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There’s no binocular in your backpack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バックパックの中に双眼鏡が見つからない。</t>
+  </si>
+  <si>
     <t xml:space="preserve">incubate</t>
   </si>
   <si>
@@ -12642,6 +12657,18 @@
   </si>
   <si>
     <t xml:space="preserve">ワァオー！全てが新鮮に感じる！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weightScale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heightMeasure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2 cm</t>
   </si>
 </sst>
 </file>
@@ -12874,7 +12901,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1020"/>
+  <dimension ref="A1:F1023"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="16.15"/>
@@ -28891,41 +28918,41 @@
         <v>3640</v>
       </c>
       <c r="B904" s="0" t="s">
-        <v>1647</v>
+        <v>3641</v>
       </c>
       <c r="D904" s="0" t="s">
-        <v>3641</v>
+        <v>3642</v>
       </c>
       <c r="E904" s="0" t="s">
-        <v>3642</v>
+        <v>3643</v>
       </c>
       <c r="F904" s="0" t="s">
-        <v>3643</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="905" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A905" s="0" t="s">
-        <v>3644</v>
+        <v>3645</v>
       </c>
       <c r="B905" s="0" t="s">
         <v>1647</v>
       </c>
       <c r="D905" s="0" t="s">
-        <v>3645</v>
+        <v>3646</v>
       </c>
       <c r="E905" s="0" t="s">
-        <v>3646</v>
+        <v>3647</v>
       </c>
       <c r="F905" s="0" t="s">
-        <v>3647</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="906" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A906" s="0" t="s">
-        <v>3648</v>
+        <v>3649</v>
       </c>
       <c r="B906" s="0" t="s">
-        <v>3649</v>
+        <v>1647</v>
       </c>
       <c r="D906" s="0" t="s">
         <v>3650</v>
@@ -28942,24 +28969,24 @@
         <v>3653</v>
       </c>
       <c r="B907" s="0" t="s">
-        <v>3649</v>
+        <v>3654</v>
       </c>
       <c r="D907" s="0" t="s">
-        <v>3654</v>
+        <v>3655</v>
       </c>
       <c r="E907" s="0" t="s">
-        <v>3655</v>
+        <v>3656</v>
       </c>
       <c r="F907" s="0" t="s">
-        <v>3656</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="908" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A908" s="0" t="s">
-        <v>3657</v>
+        <v>3658</v>
       </c>
       <c r="B908" s="0" t="s">
-        <v>3658</v>
+        <v>3654</v>
       </c>
       <c r="D908" s="0" t="s">
         <v>3659</v>
@@ -28976,24 +29003,24 @@
         <v>3662</v>
       </c>
       <c r="B909" s="0" t="s">
-        <v>518</v>
+        <v>3663</v>
       </c>
       <c r="D909" s="0" t="s">
-        <v>3663</v>
+        <v>3664</v>
       </c>
       <c r="E909" s="0" t="s">
-        <v>3664</v>
+        <v>3665</v>
       </c>
       <c r="F909" s="0" t="s">
-        <v>3665</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="910" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A910" s="0" t="s">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="B910" s="0" t="s">
-        <v>3667</v>
+        <v>518</v>
       </c>
       <c r="D910" s="0" t="s">
         <v>3668</v>
@@ -29010,75 +29037,75 @@
         <v>3671</v>
       </c>
       <c r="B911" s="0" t="s">
-        <v>3667</v>
+        <v>3672</v>
       </c>
       <c r="D911" s="0" t="s">
-        <v>3672</v>
+        <v>3673</v>
       </c>
       <c r="E911" s="0" t="s">
-        <v>3673</v>
+        <v>3674</v>
       </c>
       <c r="F911" s="0" t="s">
-        <v>3674</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="912" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A912" s="0" t="s">
-        <v>3675</v>
+        <v>3676</v>
       </c>
       <c r="B912" s="0" t="s">
-        <v>3667</v>
+        <v>3672</v>
       </c>
       <c r="D912" s="0" t="s">
-        <v>3676</v>
+        <v>3677</v>
       </c>
       <c r="E912" s="0" t="s">
-        <v>3677</v>
+        <v>3678</v>
       </c>
       <c r="F912" s="0" t="s">
-        <v>3678</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="913" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A913" s="0" t="s">
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="B913" s="0" t="s">
-        <v>3667</v>
+        <v>3672</v>
       </c>
       <c r="D913" s="0" t="s">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="E913" s="0" t="s">
-        <v>3681</v>
+        <v>3682</v>
       </c>
       <c r="F913" s="0" t="s">
-        <v>3682</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="914" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A914" s="0" t="s">
-        <v>3683</v>
+        <v>3684</v>
       </c>
       <c r="B914" s="0" t="s">
-        <v>3667</v>
+        <v>3672</v>
       </c>
       <c r="D914" s="0" t="s">
-        <v>3684</v>
+        <v>3685</v>
       </c>
       <c r="E914" s="0" t="s">
-        <v>3685</v>
+        <v>3686</v>
       </c>
       <c r="F914" s="0" t="s">
-        <v>3686</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="915" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A915" s="0" t="s">
-        <v>3687</v>
+        <v>3688</v>
       </c>
       <c r="B915" s="0" t="s">
-        <v>3688</v>
+        <v>3672</v>
       </c>
       <c r="D915" s="0" t="s">
         <v>3689</v>
@@ -29095,47 +29122,47 @@
         <v>3692</v>
       </c>
       <c r="B916" s="0" t="s">
-        <v>3268</v>
+        <v>3693</v>
       </c>
       <c r="D916" s="0" t="s">
-        <v>3693</v>
+        <v>3694</v>
       </c>
       <c r="E916" s="0" t="s">
-        <v>3694</v>
+        <v>3695</v>
       </c>
       <c r="F916" s="0" t="s">
-        <v>3695</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="917" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A917" s="0" t="s">
-        <v>3696</v>
+        <v>3697</v>
       </c>
       <c r="B917" s="0" t="s">
         <v>3268</v>
       </c>
       <c r="D917" s="0" t="s">
-        <v>3697</v>
+        <v>3698</v>
       </c>
       <c r="E917" s="0" t="s">
-        <v>3694</v>
+        <v>3699</v>
       </c>
       <c r="F917" s="0" t="s">
-        <v>3698</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="918" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A918" s="0" t="s">
+        <v>3701</v>
+      </c>
+      <c r="B918" s="0" t="s">
+        <v>3268</v>
+      </c>
+      <c r="D918" s="0" t="s">
+        <v>3702</v>
+      </c>
+      <c r="E918" s="0" t="s">
         <v>3699</v>
-      </c>
-      <c r="B918" s="0" t="s">
-        <v>3700</v>
-      </c>
-      <c r="D918" s="0" t="s">
-        <v>3701</v>
-      </c>
-      <c r="E918" s="0" t="s">
-        <v>3702</v>
       </c>
       <c r="F918" s="0" t="s">
         <v>3703</v>
@@ -29146,109 +29173,109 @@
         <v>3704</v>
       </c>
       <c r="B919" s="0" t="s">
-        <v>2720</v>
+        <v>3705</v>
       </c>
       <c r="D919" s="0" t="s">
-        <v>3705</v>
+        <v>3706</v>
       </c>
       <c r="E919" s="0" t="s">
-        <v>3706</v>
+        <v>3707</v>
       </c>
       <c r="F919" s="0" t="s">
-        <v>3707</v>
+        <v>3708</v>
       </c>
     </row>
     <row r="920" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A920" s="0" t="s">
-        <v>3708</v>
+        <v>3709</v>
       </c>
       <c r="B920" s="0" t="s">
-        <v>695</v>
+        <v>2720</v>
       </c>
       <c r="D920" s="0" t="s">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="E920" s="0" t="s">
-        <v>3710</v>
+        <v>3711</v>
       </c>
       <c r="F920" s="0" t="s">
-        <v>3711</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="921" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A921" s="0" t="s">
-        <v>3712</v>
+        <v>3713</v>
       </c>
       <c r="B921" s="0" t="s">
         <v>695</v>
       </c>
       <c r="D921" s="0" t="s">
-        <v>3713</v>
+        <v>3714</v>
       </c>
       <c r="E921" s="0" t="s">
-        <v>3714</v>
+        <v>3715</v>
       </c>
       <c r="F921" s="0" t="s">
-        <v>3715</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="922" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A922" s="0" t="s">
-        <v>3716</v>
+        <v>3717</v>
       </c>
       <c r="B922" s="0" t="s">
-        <v>40</v>
+        <v>695</v>
       </c>
       <c r="D922" s="0" t="s">
-        <v>3717</v>
+        <v>3718</v>
       </c>
       <c r="E922" s="0" t="s">
-        <v>3718</v>
+        <v>3719</v>
       </c>
       <c r="F922" s="0" t="s">
-        <v>3719</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="923" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A923" s="0" t="s">
-        <v>3720</v>
+        <v>3721</v>
       </c>
       <c r="B923" s="0" t="s">
         <v>40</v>
       </c>
       <c r="D923" s="0" t="s">
-        <v>3721</v>
+        <v>3722</v>
       </c>
       <c r="E923" s="0" t="s">
-        <v>3722</v>
+        <v>3723</v>
       </c>
       <c r="F923" s="0" t="s">
-        <v>3723</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="924" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A924" s="0" t="s">
-        <v>3724</v>
+        <v>3725</v>
       </c>
       <c r="B924" s="0" t="s">
         <v>40</v>
       </c>
       <c r="D924" s="0" t="s">
-        <v>3725</v>
+        <v>3726</v>
       </c>
       <c r="E924" s="0" t="s">
-        <v>3726</v>
+        <v>3727</v>
       </c>
       <c r="F924" s="0" t="s">
-        <v>3727</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="925" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A925" s="0" t="s">
-        <v>3728</v>
+        <v>3729</v>
       </c>
       <c r="B925" s="0" t="s">
-        <v>3729</v>
+        <v>40</v>
       </c>
       <c r="D925" s="0" t="s">
         <v>3730</v>
@@ -29265,41 +29292,41 @@
         <v>3733</v>
       </c>
       <c r="B926" s="0" t="s">
-        <v>391</v>
+        <v>3734</v>
       </c>
       <c r="D926" s="0" t="s">
-        <v>3734</v>
+        <v>3735</v>
       </c>
       <c r="E926" s="0" t="s">
-        <v>3735</v>
+        <v>3736</v>
       </c>
       <c r="F926" s="0" t="s">
-        <v>3736</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="927" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A927" s="0" t="s">
-        <v>3737</v>
+        <v>3738</v>
       </c>
       <c r="B927" s="0" t="s">
-        <v>743</v>
+        <v>391</v>
       </c>
       <c r="D927" s="0" t="s">
-        <v>3738</v>
+        <v>3739</v>
       </c>
       <c r="E927" s="0" t="s">
-        <v>3739</v>
+        <v>3740</v>
       </c>
       <c r="F927" s="0" t="s">
-        <v>3740</v>
+        <v>3741</v>
       </c>
     </row>
     <row r="928" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A928" s="0" t="s">
-        <v>3741</v>
+        <v>3742</v>
       </c>
       <c r="B928" s="0" t="s">
-        <v>3742</v>
+        <v>743</v>
       </c>
       <c r="D928" s="0" t="s">
         <v>3743</v>
@@ -29316,109 +29343,109 @@
         <v>3746</v>
       </c>
       <c r="B929" s="0" t="s">
-        <v>3742</v>
+        <v>3747</v>
       </c>
       <c r="D929" s="0" t="s">
-        <v>3747</v>
+        <v>3748</v>
       </c>
       <c r="E929" s="0" t="s">
-        <v>3748</v>
+        <v>3749</v>
       </c>
       <c r="F929" s="0" t="s">
-        <v>3749</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="930" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A930" s="0" t="s">
-        <v>3750</v>
+        <v>3751</v>
       </c>
       <c r="B930" s="0" t="s">
-        <v>3742</v>
+        <v>3747</v>
       </c>
       <c r="D930" s="0" t="s">
-        <v>1845</v>
+        <v>3752</v>
       </c>
       <c r="E930" s="0" t="s">
-        <v>3751</v>
+        <v>3753</v>
       </c>
       <c r="F930" s="0" t="s">
-        <v>1847</v>
+        <v>3754</v>
       </c>
     </row>
     <row r="931" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A931" s="0" t="s">
-        <v>3752</v>
+        <v>3755</v>
       </c>
       <c r="B931" s="0" t="s">
-        <v>134</v>
+        <v>3747</v>
       </c>
       <c r="D931" s="0" t="s">
-        <v>3753</v>
+        <v>1845</v>
       </c>
       <c r="E931" s="0" t="s">
-        <v>3754</v>
+        <v>3756</v>
       </c>
       <c r="F931" s="0" t="s">
-        <v>3755</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="932" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A932" s="0" t="s">
-        <v>3756</v>
+        <v>3757</v>
       </c>
       <c r="B932" s="0" t="s">
         <v>134</v>
       </c>
       <c r="D932" s="0" t="s">
-        <v>3757</v>
+        <v>3758</v>
       </c>
       <c r="E932" s="0" t="s">
-        <v>3758</v>
+        <v>3759</v>
       </c>
       <c r="F932" s="0" t="s">
-        <v>3759</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="933" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A933" s="0" t="s">
-        <v>3760</v>
+        <v>3761</v>
       </c>
       <c r="B933" s="0" t="s">
-        <v>1282</v>
+        <v>134</v>
       </c>
       <c r="D933" s="0" t="s">
-        <v>3761</v>
+        <v>3762</v>
       </c>
       <c r="E933" s="0" t="s">
-        <v>3762</v>
+        <v>3763</v>
       </c>
       <c r="F933" s="0" t="s">
-        <v>3763</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="934" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A934" s="0" t="s">
-        <v>3764</v>
+        <v>3765</v>
       </c>
       <c r="B934" s="0" t="s">
         <v>1282</v>
       </c>
       <c r="D934" s="0" t="s">
-        <v>3765</v>
+        <v>3766</v>
       </c>
       <c r="E934" s="0" t="s">
-        <v>3766</v>
+        <v>3767</v>
       </c>
       <c r="F934" s="0" t="s">
-        <v>3767</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="935" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A935" s="0" t="s">
-        <v>3768</v>
+        <v>3769</v>
       </c>
       <c r="B935" s="0" t="s">
-        <v>3769</v>
+        <v>1282</v>
       </c>
       <c r="D935" s="0" t="s">
         <v>3770</v>
@@ -29435,24 +29462,24 @@
         <v>3773</v>
       </c>
       <c r="B936" s="0" t="s">
-        <v>3769</v>
+        <v>3774</v>
       </c>
       <c r="D936" s="0" t="s">
-        <v>3774</v>
+        <v>3775</v>
       </c>
       <c r="E936" s="0" t="s">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="F936" s="0" t="s">
-        <v>3776</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="937" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A937" s="0" t="s">
-        <v>3777</v>
+        <v>3778</v>
       </c>
       <c r="B937" s="0" t="s">
-        <v>3778</v>
+        <v>3774</v>
       </c>
       <c r="D937" s="0" t="s">
         <v>3779</v>
@@ -29469,228 +29496,228 @@
         <v>3782</v>
       </c>
       <c r="B938" s="0" t="s">
-        <v>3778</v>
+        <v>3783</v>
       </c>
       <c r="D938" s="0" t="s">
-        <v>3783</v>
+        <v>3784</v>
       </c>
       <c r="E938" s="0" t="s">
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="F938" s="0" t="s">
-        <v>3785</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="939" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A939" s="0" t="s">
-        <v>3786</v>
+        <v>3787</v>
       </c>
       <c r="B939" s="0" t="s">
-        <v>3778</v>
+        <v>3783</v>
       </c>
       <c r="D939" s="0" t="s">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="E939" s="0" t="s">
-        <v>3788</v>
+        <v>3789</v>
       </c>
       <c r="F939" s="0" t="s">
-        <v>3789</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="940" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A940" s="0" t="s">
-        <v>3790</v>
+        <v>3791</v>
       </c>
       <c r="B940" s="0" t="s">
-        <v>3778</v>
+        <v>3783</v>
       </c>
       <c r="D940" s="0" t="s">
-        <v>3791</v>
+        <v>3792</v>
       </c>
       <c r="E940" s="0" t="s">
-        <v>3792</v>
+        <v>3793</v>
       </c>
       <c r="F940" s="0" t="s">
-        <v>3793</v>
+        <v>3794</v>
       </c>
     </row>
     <row r="941" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A941" s="0" t="s">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="B941" s="0" t="s">
-        <v>3778</v>
+        <v>3783</v>
       </c>
       <c r="D941" s="0" t="s">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="E941" s="0" t="s">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="F941" s="0" t="s">
-        <v>3797</v>
+        <v>3798</v>
       </c>
     </row>
     <row r="942" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A942" s="0" t="s">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="B942" s="0" t="s">
-        <v>3778</v>
+        <v>3783</v>
       </c>
       <c r="D942" s="0" t="s">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="E942" s="0" t="s">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="F942" s="0" t="s">
-        <v>3801</v>
+        <v>3802</v>
       </c>
     </row>
     <row r="943" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A943" s="0" t="s">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="B943" s="0" t="s">
-        <v>3778</v>
+        <v>3783</v>
       </c>
       <c r="D943" s="0" t="s">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="E943" s="0" t="s">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="F943" s="0" t="s">
-        <v>3805</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="944" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A944" s="0" t="s">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="B944" s="0" t="s">
-        <v>627</v>
+        <v>3783</v>
       </c>
       <c r="D944" s="0" t="s">
-        <v>3807</v>
+        <v>3808</v>
       </c>
       <c r="E944" s="0" t="s">
-        <v>3808</v>
+        <v>3809</v>
       </c>
       <c r="F944" s="0" t="s">
-        <v>3809</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="945" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A945" s="0" t="s">
-        <v>3810</v>
+        <v>3811</v>
       </c>
       <c r="B945" s="0" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="D945" s="0" t="s">
-        <v>3811</v>
+        <v>3812</v>
       </c>
       <c r="E945" s="0" t="s">
-        <v>3812</v>
+        <v>3813</v>
       </c>
       <c r="F945" s="0" t="s">
-        <v>3813</v>
+        <v>3814</v>
       </c>
     </row>
     <row r="946" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A946" s="0" t="s">
-        <v>3814</v>
+        <v>3815</v>
       </c>
       <c r="B946" s="0" t="s">
         <v>618</v>
       </c>
       <c r="D946" s="0" t="s">
-        <v>3815</v>
+        <v>3816</v>
       </c>
       <c r="E946" s="0" t="s">
-        <v>3816</v>
+        <v>3817</v>
       </c>
       <c r="F946" s="0" t="s">
-        <v>3817</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="947" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A947" s="0" t="s">
-        <v>3818</v>
+        <v>3819</v>
       </c>
       <c r="B947" s="0" t="s">
-        <v>1159</v>
+        <v>618</v>
       </c>
       <c r="D947" s="0" t="s">
-        <v>3819</v>
+        <v>3820</v>
       </c>
       <c r="E947" s="0" t="s">
-        <v>3820</v>
+        <v>3821</v>
       </c>
       <c r="F947" s="0" t="s">
-        <v>3821</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="948" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A948" s="0" t="s">
-        <v>3822</v>
+        <v>3823</v>
       </c>
       <c r="B948" s="0" t="s">
         <v>1159</v>
       </c>
       <c r="D948" s="0" t="s">
-        <v>3823</v>
+        <v>3824</v>
       </c>
       <c r="E948" s="0" t="s">
-        <v>3824</v>
+        <v>3825</v>
       </c>
       <c r="F948" s="0" t="s">
-        <v>3825</v>
-      </c>
-    </row>
-    <row r="949" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3826</v>
+      </c>
+    </row>
+    <row r="949" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A949" s="0" t="s">
-        <v>3826</v>
+        <v>3827</v>
       </c>
       <c r="B949" s="0" t="s">
         <v>1159</v>
       </c>
-      <c r="D949" s="2" t="s">
-        <v>3827</v>
-      </c>
-      <c r="E949" s="2" t="s">
+      <c r="D949" s="0" t="s">
         <v>3828</v>
       </c>
-      <c r="F949" s="2" t="s">
+      <c r="E949" s="0" t="s">
         <v>3829</v>
       </c>
-    </row>
-    <row r="950" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F949" s="0" t="s">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="950" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A950" s="0" t="s">
-        <v>3830</v>
+        <v>3831</v>
       </c>
       <c r="B950" s="0" t="s">
         <v>1159</v>
       </c>
-      <c r="D950" s="0" t="s">
-        <v>3831</v>
-      </c>
-      <c r="E950" s="0" t="s">
+      <c r="D950" s="2" t="s">
         <v>3832</v>
       </c>
-      <c r="F950" s="0" t="s">
+      <c r="E950" s="2" t="s">
         <v>3833</v>
+      </c>
+      <c r="F950" s="2" t="s">
+        <v>3834</v>
       </c>
     </row>
     <row r="951" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A951" s="0" t="s">
-        <v>3834</v>
+        <v>3835</v>
       </c>
       <c r="B951" s="0" t="s">
-        <v>3835</v>
+        <v>1159</v>
       </c>
       <c r="D951" s="0" t="s">
         <v>3836</v>
@@ -29724,58 +29751,58 @@
         <v>3844</v>
       </c>
       <c r="B953" s="0" t="s">
-        <v>2609</v>
+        <v>3845</v>
       </c>
       <c r="D953" s="0" t="s">
-        <v>3845</v>
+        <v>3846</v>
       </c>
       <c r="E953" s="0" t="s">
-        <v>3846</v>
+        <v>3847</v>
       </c>
       <c r="F953" s="0" t="s">
-        <v>3847</v>
+        <v>3848</v>
       </c>
     </row>
     <row r="954" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A954" s="0" t="s">
-        <v>3848</v>
+        <v>3849</v>
       </c>
       <c r="B954" s="0" t="s">
         <v>2609</v>
       </c>
       <c r="D954" s="0" t="s">
-        <v>3849</v>
+        <v>3850</v>
       </c>
       <c r="E954" s="0" t="s">
-        <v>3850</v>
+        <v>3851</v>
       </c>
       <c r="F954" s="0" t="s">
-        <v>3851</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="955" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A955" s="0" t="s">
-        <v>3852</v>
+        <v>3853</v>
       </c>
       <c r="B955" s="0" t="s">
         <v>2609</v>
       </c>
       <c r="D955" s="0" t="s">
-        <v>3853</v>
+        <v>3854</v>
       </c>
       <c r="E955" s="0" t="s">
-        <v>3854</v>
+        <v>3855</v>
       </c>
       <c r="F955" s="0" t="s">
-        <v>3855</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="956" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A956" s="0" t="s">
-        <v>3856</v>
+        <v>3857</v>
       </c>
       <c r="B956" s="0" t="s">
-        <v>3857</v>
+        <v>2609</v>
       </c>
       <c r="D956" s="0" t="s">
         <v>3858</v>
@@ -29860,126 +29887,126 @@
         <v>3881</v>
       </c>
       <c r="B961" s="0" t="s">
-        <v>224</v>
+        <v>3882</v>
       </c>
       <c r="D961" s="0" t="s">
-        <v>3882</v>
+        <v>3883</v>
       </c>
       <c r="E961" s="0" t="s">
-        <v>3883</v>
+        <v>3884</v>
       </c>
       <c r="F961" s="0" t="s">
-        <v>3884</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="962" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A962" s="0" t="s">
-        <v>3885</v>
+        <v>3886</v>
       </c>
       <c r="B962" s="0" t="s">
         <v>224</v>
       </c>
       <c r="D962" s="0" t="s">
-        <v>3886</v>
+        <v>3887</v>
       </c>
       <c r="E962" s="0" t="s">
-        <v>3887</v>
+        <v>3888</v>
       </c>
       <c r="F962" s="0" t="s">
-        <v>3888</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="963" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A963" s="0" t="s">
-        <v>3889</v>
+        <v>3890</v>
       </c>
       <c r="B963" s="0" t="s">
         <v>224</v>
       </c>
       <c r="D963" s="0" t="s">
-        <v>3890</v>
+        <v>3891</v>
       </c>
       <c r="E963" s="0" t="s">
-        <v>3891</v>
+        <v>3892</v>
       </c>
       <c r="F963" s="0" t="s">
-        <v>3892</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="964" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A964" s="0" t="s">
-        <v>3893</v>
+        <v>3894</v>
       </c>
       <c r="B964" s="0" t="s">
         <v>224</v>
       </c>
       <c r="D964" s="0" t="s">
-        <v>3894</v>
+        <v>3895</v>
       </c>
       <c r="E964" s="0" t="s">
-        <v>3895</v>
+        <v>3896</v>
       </c>
       <c r="F964" s="0" t="s">
-        <v>3896</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="965" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A965" s="0" t="s">
-        <v>3897</v>
+        <v>3898</v>
       </c>
       <c r="B965" s="0" t="s">
-        <v>288</v>
+        <v>224</v>
       </c>
       <c r="D965" s="0" t="s">
-        <v>3898</v>
+        <v>3899</v>
       </c>
       <c r="E965" s="0" t="s">
-        <v>3899</v>
+        <v>3900</v>
       </c>
       <c r="F965" s="0" t="s">
-        <v>3900</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="966" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A966" s="0" t="s">
-        <v>3901</v>
+        <v>3902</v>
       </c>
       <c r="B966" s="0" t="s">
         <v>288</v>
       </c>
       <c r="D966" s="0" t="s">
-        <v>3902</v>
+        <v>3903</v>
       </c>
       <c r="E966" s="0" t="s">
-        <v>3903</v>
+        <v>3904</v>
       </c>
       <c r="F966" s="0" t="s">
-        <v>3904</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="967" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A967" s="0" t="s">
-        <v>3905</v>
+        <v>3906</v>
       </c>
       <c r="B967" s="0" t="s">
         <v>288</v>
       </c>
       <c r="D967" s="0" t="s">
-        <v>3906</v>
+        <v>3907</v>
       </c>
       <c r="E967" s="0" t="s">
-        <v>3907</v>
+        <v>3908</v>
       </c>
       <c r="F967" s="0" t="s">
-        <v>3908</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="968" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A968" s="0" t="s">
-        <v>3909</v>
+        <v>3910</v>
       </c>
       <c r="B968" s="0" t="s">
-        <v>3910</v>
+        <v>288</v>
       </c>
       <c r="D968" s="0" t="s">
         <v>3911</v>
@@ -29996,92 +30023,92 @@
         <v>3914</v>
       </c>
       <c r="B969" s="0" t="s">
-        <v>3910</v>
+        <v>3915</v>
       </c>
       <c r="D969" s="0" t="s">
-        <v>3911</v>
+        <v>3916</v>
       </c>
       <c r="E969" s="0" t="s">
-        <v>3912</v>
+        <v>3917</v>
       </c>
       <c r="F969" s="0" t="s">
-        <v>3913</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="970" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A970" s="0" t="s">
+        <v>3919</v>
+      </c>
+      <c r="B970" s="0" t="s">
         <v>3915</v>
       </c>
-      <c r="B970" s="0" t="s">
-        <v>3910</v>
-      </c>
       <c r="D970" s="0" t="s">
-        <v>3911</v>
+        <v>3916</v>
       </c>
       <c r="E970" s="0" t="s">
-        <v>3912</v>
+        <v>3917</v>
       </c>
       <c r="F970" s="0" t="s">
-        <v>3913</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="971" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A971" s="0" t="s">
+        <v>3920</v>
+      </c>
+      <c r="B971" s="0" t="s">
+        <v>3915</v>
+      </c>
+      <c r="D971" s="0" t="s">
         <v>3916</v>
       </c>
-      <c r="B971" s="0" t="s">
-        <v>3910</v>
-      </c>
-      <c r="D971" s="0" t="s">
+      <c r="E971" s="0" t="s">
         <v>3917</v>
       </c>
-      <c r="E971" s="0" t="s">
+      <c r="F971" s="0" t="s">
         <v>3918</v>
-      </c>
-      <c r="F971" s="0" t="s">
-        <v>3919</v>
       </c>
     </row>
     <row r="972" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A972" s="0" t="s">
-        <v>3920</v>
+        <v>3921</v>
       </c>
       <c r="B972" s="0" t="s">
-        <v>288</v>
+        <v>3915</v>
       </c>
       <c r="D972" s="0" t="s">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="E972" s="0" t="s">
-        <v>3922</v>
+        <v>3923</v>
       </c>
       <c r="F972" s="0" t="s">
-        <v>3923</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="973" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A973" s="0" t="s">
-        <v>3924</v>
+        <v>3925</v>
       </c>
       <c r="B973" s="0" t="s">
-        <v>2969</v>
+        <v>288</v>
       </c>
       <c r="D973" s="0" t="s">
-        <v>3925</v>
+        <v>3926</v>
       </c>
       <c r="E973" s="0" t="s">
-        <v>3926</v>
+        <v>3927</v>
       </c>
       <c r="F973" s="0" t="s">
-        <v>3927</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="974" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A974" s="0" t="s">
-        <v>3928</v>
+        <v>3929</v>
       </c>
       <c r="B974" s="0" t="s">
-        <v>3929</v>
+        <v>2969</v>
       </c>
       <c r="D974" s="0" t="s">
         <v>3930</v>
@@ -30093,199 +30120,199 @@
         <v>3932</v>
       </c>
     </row>
-    <row r="975" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="975" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A975" s="0" t="s">
         <v>3933</v>
       </c>
       <c r="B975" s="0" t="s">
         <v>3934</v>
       </c>
-      <c r="D975" s="2" t="s">
+      <c r="D975" s="0" t="s">
         <v>3935</v>
       </c>
-      <c r="E975" s="2" t="s">
+      <c r="E975" s="0" t="s">
         <v>3936</v>
       </c>
-      <c r="F975" s="2" t="s">
+      <c r="F975" s="0" t="s">
         <v>3937</v>
       </c>
     </row>
-    <row r="976" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="976" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A976" s="0" t="s">
         <v>3938</v>
       </c>
       <c r="B976" s="0" t="s">
-        <v>3380</v>
+        <v>3939</v>
       </c>
       <c r="D976" s="2" t="s">
-        <v>3939</v>
+        <v>3940</v>
       </c>
       <c r="E976" s="2" t="s">
-        <v>3940</v>
+        <v>3941</v>
       </c>
       <c r="F976" s="2" t="s">
-        <v>3941</v>
-      </c>
-    </row>
-    <row r="977" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="977" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A977" s="0" t="s">
-        <v>3942</v>
+        <v>3943</v>
       </c>
       <c r="B977" s="0" t="s">
         <v>3380</v>
       </c>
-      <c r="D977" s="0" t="s">
-        <v>3943</v>
-      </c>
-      <c r="E977" s="0" t="s">
+      <c r="D977" s="2" t="s">
         <v>3944</v>
       </c>
-      <c r="F977" s="0" t="s">
+      <c r="E977" s="2" t="s">
         <v>3945</v>
+      </c>
+      <c r="F977" s="2" t="s">
+        <v>3946</v>
       </c>
     </row>
     <row r="978" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A978" s="0" t="s">
-        <v>3946</v>
+        <v>3947</v>
       </c>
       <c r="B978" s="0" t="s">
         <v>3380</v>
       </c>
       <c r="D978" s="0" t="s">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="E978" s="0" t="s">
-        <v>3948</v>
+        <v>3949</v>
       </c>
       <c r="F978" s="0" t="s">
-        <v>3949</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="979" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A979" s="0" t="s">
-        <v>3950</v>
+        <v>3951</v>
       </c>
       <c r="B979" s="0" t="s">
         <v>3380</v>
       </c>
       <c r="D979" s="0" t="s">
-        <v>3951</v>
+        <v>3952</v>
       </c>
       <c r="E979" s="0" t="s">
-        <v>3952</v>
+        <v>3953</v>
       </c>
       <c r="F979" s="0" t="s">
-        <v>3953</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="980" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A980" s="0" t="s">
-        <v>3954</v>
+        <v>3955</v>
       </c>
       <c r="B980" s="0" t="s">
-        <v>870</v>
+        <v>3380</v>
       </c>
       <c r="D980" s="0" t="s">
-        <v>3955</v>
+        <v>3956</v>
       </c>
       <c r="E980" s="0" t="s">
-        <v>3956</v>
+        <v>3957</v>
       </c>
       <c r="F980" s="0" t="s">
-        <v>3957</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="981" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A981" s="0" t="s">
-        <v>3958</v>
+        <v>3959</v>
       </c>
       <c r="B981" s="0" t="s">
         <v>870</v>
       </c>
       <c r="D981" s="0" t="s">
-        <v>3959</v>
+        <v>3960</v>
       </c>
       <c r="E981" s="0" t="s">
-        <v>3960</v>
+        <v>3961</v>
       </c>
       <c r="F981" s="0" t="s">
-        <v>3961</v>
-      </c>
-    </row>
-    <row r="982" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3962</v>
+      </c>
+    </row>
+    <row r="982" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A982" s="0" t="s">
-        <v>3962</v>
+        <v>3963</v>
       </c>
       <c r="B982" s="0" t="s">
         <v>870</v>
       </c>
-      <c r="D982" s="2" t="s">
-        <v>3963</v>
-      </c>
-      <c r="E982" s="2" t="s">
+      <c r="D982" s="0" t="s">
         <v>3964</v>
       </c>
-      <c r="F982" s="2" t="s">
+      <c r="E982" s="0" t="s">
         <v>3965</v>
       </c>
-    </row>
-    <row r="983" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F982" s="0" t="s">
+        <v>3966</v>
+      </c>
+    </row>
+    <row r="983" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A983" s="0" t="s">
-        <v>3966</v>
+        <v>3967</v>
       </c>
       <c r="B983" s="0" t="s">
         <v>870</v>
       </c>
-      <c r="D983" s="0" t="s">
-        <v>3967</v>
-      </c>
-      <c r="E983" s="0" t="s">
+      <c r="D983" s="2" t="s">
         <v>3968</v>
       </c>
-      <c r="F983" s="0" t="s">
+      <c r="E983" s="2" t="s">
         <v>3969</v>
       </c>
-    </row>
-    <row r="984" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F983" s="2" t="s">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="984" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A984" s="0" t="s">
-        <v>3970</v>
+        <v>3971</v>
       </c>
       <c r="B984" s="0" t="s">
         <v>870</v>
       </c>
-      <c r="D984" s="2" t="s">
-        <v>3971</v>
-      </c>
-      <c r="E984" s="2" t="s">
+      <c r="D984" s="0" t="s">
         <v>3972</v>
       </c>
-      <c r="F984" s="2" t="s">
+      <c r="E984" s="0" t="s">
         <v>3973</v>
       </c>
-    </row>
-    <row r="985" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F984" s="0" t="s">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="985" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A985" s="0" t="s">
-        <v>3974</v>
+        <v>3975</v>
       </c>
       <c r="B985" s="0" t="s">
-        <v>3910</v>
-      </c>
-      <c r="D985" s="0" t="s">
-        <v>3975</v>
-      </c>
-      <c r="E985" s="0" t="s">
+        <v>870</v>
+      </c>
+      <c r="D985" s="2" t="s">
         <v>3976</v>
       </c>
-      <c r="F985" s="0" t="s">
+      <c r="E985" s="2" t="s">
         <v>3977</v>
+      </c>
+      <c r="F985" s="2" t="s">
+        <v>3978</v>
       </c>
     </row>
     <row r="986" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A986" s="0" t="s">
-        <v>3978</v>
+        <v>3979</v>
       </c>
       <c r="B986" s="0" t="s">
-        <v>3979</v>
+        <v>3915</v>
       </c>
       <c r="D986" s="0" t="s">
         <v>3980</v>
@@ -30302,140 +30329,140 @@
         <v>3983</v>
       </c>
       <c r="B987" s="0" t="s">
-        <v>3910</v>
+        <v>3984</v>
       </c>
       <c r="D987" s="0" t="s">
-        <v>3984</v>
+        <v>3985</v>
       </c>
       <c r="E987" s="0" t="s">
-        <v>3985</v>
+        <v>3986</v>
       </c>
       <c r="F987" s="0" t="s">
-        <v>3986</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="988" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A988" s="0" t="s">
-        <v>3987</v>
+        <v>3988</v>
       </c>
       <c r="B988" s="0" t="s">
+        <v>3915</v>
+      </c>
+      <c r="D988" s="0" t="s">
+        <v>3989</v>
+      </c>
+      <c r="E988" s="0" t="s">
+        <v>3990</v>
+      </c>
+      <c r="F988" s="0" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="989" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A989" s="0" t="s">
+        <v>3992</v>
+      </c>
+      <c r="B989" s="0" t="s">
         <v>641</v>
       </c>
-      <c r="D988" s="0" t="s">
-        <v>3988</v>
-      </c>
-      <c r="E988" s="0" t="s">
-        <v>3989</v>
-      </c>
-      <c r="F988" s="0" t="s">
-        <v>3990</v>
-      </c>
-    </row>
-    <row r="989" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A989" s="0" t="s">
-        <v>3991</v>
-      </c>
-      <c r="B989" s="0" t="s">
-        <v>3910</v>
-      </c>
-      <c r="D989" s="2" t="s">
-        <v>3992</v>
-      </c>
-      <c r="E989" s="2" t="s">
+      <c r="D989" s="0" t="s">
         <v>3993</v>
       </c>
-      <c r="F989" s="2" t="s">
+      <c r="E989" s="0" t="s">
         <v>3994</v>
       </c>
-    </row>
-    <row r="990" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F989" s="0" t="s">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="990" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A990" s="0" t="s">
-        <v>3995</v>
+        <v>3996</v>
       </c>
       <c r="B990" s="0" t="s">
-        <v>3910</v>
-      </c>
-      <c r="D990" s="0" t="s">
-        <v>3996</v>
-      </c>
-      <c r="E990" s="0" t="s">
+        <v>3915</v>
+      </c>
+      <c r="D990" s="2" t="s">
         <v>3997</v>
       </c>
-      <c r="F990" s="0" t="s">
+      <c r="E990" s="2" t="s">
         <v>3998</v>
+      </c>
+      <c r="F990" s="2" t="s">
+        <v>3999</v>
       </c>
     </row>
     <row r="991" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A991" s="0" t="s">
-        <v>3999</v>
+        <v>4000</v>
       </c>
       <c r="B991" s="0" t="s">
-        <v>3910</v>
+        <v>3915</v>
       </c>
       <c r="D991" s="0" t="s">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="E991" s="0" t="s">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="F991" s="0" t="s">
-        <v>4002</v>
+        <v>4003</v>
       </c>
     </row>
     <row r="992" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A992" s="0" t="s">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="B992" s="0" t="s">
-        <v>641</v>
+        <v>3915</v>
       </c>
       <c r="D992" s="0" t="s">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="E992" s="0" t="s">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="F992" s="0" t="s">
-        <v>4006</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="993" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A993" s="0" t="s">
-        <v>4007</v>
+        <v>4008</v>
       </c>
       <c r="B993" s="0" t="s">
         <v>641</v>
       </c>
       <c r="D993" s="0" t="s">
-        <v>4008</v>
+        <v>4009</v>
       </c>
       <c r="E993" s="0" t="s">
-        <v>4009</v>
+        <v>4010</v>
       </c>
       <c r="F993" s="0" t="s">
-        <v>4010</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="994" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A994" s="0" t="s">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="B994" s="0" t="s">
         <v>641</v>
       </c>
       <c r="D994" s="0" t="s">
-        <v>4008</v>
+        <v>4013</v>
       </c>
       <c r="E994" s="0" t="s">
-        <v>4009</v>
+        <v>4014</v>
       </c>
       <c r="F994" s="0" t="s">
-        <v>4010</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="995" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A995" s="0" t="s">
-        <v>4012</v>
+        <v>4016</v>
       </c>
       <c r="B995" s="0" t="s">
         <v>641</v>
@@ -30452,24 +30479,24 @@
     </row>
     <row r="996" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A996" s="0" t="s">
-        <v>4016</v>
+        <v>4017</v>
       </c>
       <c r="B996" s="0" t="s">
         <v>641</v>
       </c>
       <c r="D996" s="0" t="s">
-        <v>4013</v>
+        <v>4018</v>
       </c>
       <c r="E996" s="0" t="s">
-        <v>4014</v>
+        <v>4019</v>
       </c>
       <c r="F996" s="0" t="s">
-        <v>4015</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="997" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A997" s="0" t="s">
-        <v>4017</v>
+        <v>4021</v>
       </c>
       <c r="B997" s="0" t="s">
         <v>641</v>
@@ -30486,10 +30513,10 @@
     </row>
     <row r="998" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A998" s="0" t="s">
-        <v>4021</v>
+        <v>4022</v>
       </c>
       <c r="B998" s="0" t="s">
-        <v>4022</v>
+        <v>641</v>
       </c>
       <c r="D998" s="0" t="s">
         <v>4023</v>
@@ -30506,373 +30533,424 @@
         <v>4026</v>
       </c>
       <c r="B999" s="0" t="s">
-        <v>3258</v>
+        <v>4027</v>
       </c>
       <c r="D999" s="0" t="s">
-        <v>4027</v>
+        <v>4028</v>
       </c>
       <c r="E999" s="0" t="s">
-        <v>4028</v>
+        <v>4029</v>
       </c>
       <c r="F999" s="0" t="s">
-        <v>4029</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="1000" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1000" s="0" t="s">
-        <v>4030</v>
+        <v>4031</v>
       </c>
       <c r="B1000" s="0" t="s">
-        <v>4022</v>
+        <v>3258</v>
       </c>
       <c r="D1000" s="0" t="s">
-        <v>4031</v>
+        <v>4032</v>
       </c>
       <c r="E1000" s="0" t="s">
-        <v>4032</v>
+        <v>4033</v>
       </c>
       <c r="F1000" s="0" t="s">
-        <v>4033</v>
+        <v>4034</v>
       </c>
     </row>
     <row r="1001" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1001" s="0" t="s">
-        <v>4034</v>
+        <v>4035</v>
       </c>
       <c r="B1001" s="0" t="s">
-        <v>4022</v>
+        <v>4027</v>
       </c>
       <c r="D1001" s="0" t="s">
-        <v>4035</v>
+        <v>4036</v>
       </c>
       <c r="E1001" s="0" t="s">
-        <v>4036</v>
+        <v>4037</v>
       </c>
       <c r="F1001" s="0" t="s">
-        <v>4037</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="1002" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1002" s="0" t="s">
-        <v>4038</v>
+        <v>4039</v>
       </c>
       <c r="B1002" s="0" t="s">
-        <v>4022</v>
+        <v>4027</v>
       </c>
       <c r="D1002" s="0" t="s">
-        <v>4039</v>
+        <v>4040</v>
       </c>
       <c r="E1002" s="0" t="s">
-        <v>4040</v>
+        <v>4041</v>
       </c>
       <c r="F1002" s="0" t="s">
-        <v>4041</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="1003" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1003" s="0" t="s">
-        <v>4042</v>
+        <v>4043</v>
       </c>
       <c r="B1003" s="0" t="s">
-        <v>2396</v>
+        <v>4027</v>
       </c>
       <c r="D1003" s="0" t="s">
-        <v>4043</v>
+        <v>4044</v>
       </c>
       <c r="E1003" s="0" t="s">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="F1003" s="0" t="s">
-        <v>4045</v>
+        <v>4046</v>
       </c>
     </row>
     <row r="1004" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1004" s="0" t="s">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="B1004" s="0" t="s">
         <v>2396</v>
       </c>
       <c r="D1004" s="0" t="s">
-        <v>4047</v>
+        <v>4048</v>
       </c>
       <c r="E1004" s="0" t="s">
-        <v>4048</v>
+        <v>4049</v>
       </c>
       <c r="F1004" s="0" t="s">
-        <v>4049</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="1005" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1005" s="0" t="s">
-        <v>4050</v>
+        <v>4051</v>
       </c>
       <c r="B1005" s="0" t="s">
         <v>2396</v>
       </c>
       <c r="D1005" s="0" t="s">
-        <v>4051</v>
+        <v>4052</v>
       </c>
       <c r="E1005" s="0" t="s">
-        <v>4052</v>
+        <v>4053</v>
       </c>
       <c r="F1005" s="0" t="s">
-        <v>4053</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="1006" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1006" s="0" t="s">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="B1006" s="0" t="s">
         <v>2396</v>
       </c>
       <c r="D1006" s="0" t="s">
-        <v>4055</v>
+        <v>4056</v>
       </c>
       <c r="E1006" s="0" t="s">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="F1006" s="0" t="s">
-        <v>4057</v>
+        <v>4058</v>
       </c>
     </row>
     <row r="1007" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1007" s="0" t="s">
-        <v>4058</v>
+        <v>4059</v>
       </c>
       <c r="B1007" s="0" t="s">
-        <v>2891</v>
+        <v>2396</v>
       </c>
       <c r="D1007" s="0" t="s">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="E1007" s="0" t="s">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="F1007" s="0" t="s">
-        <v>4061</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="1008" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1008" s="0" t="s">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B1008" s="0" t="s">
-        <v>182</v>
+        <v>2891</v>
       </c>
       <c r="D1008" s="0" t="s">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="E1008" s="0" t="s">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="F1008" s="0" t="s">
-        <v>4065</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1009" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1009" s="0" t="s">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="B1009" s="0" t="s">
         <v>182</v>
       </c>
       <c r="D1009" s="0" t="s">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="E1009" s="0" t="s">
-        <v>4068</v>
+        <v>4069</v>
       </c>
       <c r="F1009" s="0" t="s">
-        <v>4069</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1010" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1010" s="0" t="s">
-        <v>4070</v>
+        <v>4071</v>
       </c>
       <c r="B1010" s="0" t="s">
         <v>182</v>
       </c>
       <c r="D1010" s="0" t="s">
-        <v>4071</v>
+        <v>4072</v>
       </c>
       <c r="E1010" s="0" t="s">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="F1010" s="0" t="s">
-        <v>4073</v>
+        <v>4074</v>
       </c>
     </row>
     <row r="1011" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1011" s="0" t="s">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="B1011" s="0" t="s">
         <v>182</v>
       </c>
       <c r="D1011" s="0" t="s">
-        <v>4075</v>
+        <v>4076</v>
       </c>
       <c r="E1011" s="0" t="s">
-        <v>4076</v>
+        <v>4077</v>
       </c>
       <c r="F1011" s="0" t="s">
-        <v>4077</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1012" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1012" s="0" t="s">
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="B1012" s="0" t="s">
         <v>182</v>
       </c>
       <c r="D1012" s="0" t="s">
-        <v>4079</v>
+        <v>4080</v>
       </c>
       <c r="E1012" s="0" t="s">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="F1012" s="0" t="s">
-        <v>4081</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="1013" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1013" s="0" t="s">
-        <v>4082</v>
+        <v>4083</v>
       </c>
       <c r="B1013" s="0" t="s">
         <v>182</v>
       </c>
       <c r="D1013" s="0" t="s">
-        <v>4083</v>
+        <v>4084</v>
       </c>
       <c r="E1013" s="0" t="s">
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="F1013" s="0" t="s">
-        <v>4085</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="1014" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1014" s="0" t="s">
-        <v>4086</v>
+        <v>4087</v>
       </c>
       <c r="B1014" s="0" t="s">
         <v>182</v>
       </c>
       <c r="D1014" s="0" t="s">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="E1014" s="0" t="s">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="F1014" s="0" t="s">
-        <v>4089</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="1015" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1015" s="0" t="s">
-        <v>4090</v>
+        <v>4091</v>
       </c>
       <c r="B1015" s="0" t="s">
         <v>182</v>
       </c>
       <c r="D1015" s="0" t="s">
-        <v>4091</v>
+        <v>4092</v>
       </c>
       <c r="E1015" s="0" t="s">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="F1015" s="0" t="s">
-        <v>4093</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="1016" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1016" s="0" t="s">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="B1016" s="0" t="s">
-        <v>3258</v>
+        <v>182</v>
       </c>
       <c r="D1016" s="0" t="s">
-        <v>4095</v>
+        <v>4096</v>
       </c>
       <c r="E1016" s="0" t="s">
-        <v>4096</v>
+        <v>4097</v>
       </c>
       <c r="F1016" s="0" t="s">
-        <v>4097</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="1017" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1017" s="0" t="s">
-        <v>4098</v>
+        <v>4099</v>
       </c>
       <c r="B1017" s="0" t="s">
         <v>3258</v>
       </c>
       <c r="D1017" s="0" t="s">
-        <v>4099</v>
+        <v>4100</v>
       </c>
       <c r="E1017" s="0" t="s">
-        <v>4100</v>
+        <v>4101</v>
       </c>
       <c r="F1017" s="0" t="s">
-        <v>4101</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="1018" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1018" s="0" t="s">
-        <v>4102</v>
+        <v>4103</v>
       </c>
       <c r="B1018" s="0" t="s">
-        <v>658</v>
+        <v>3258</v>
       </c>
       <c r="D1018" s="0" t="s">
-        <v>4103</v>
+        <v>4104</v>
       </c>
       <c r="E1018" s="0" t="s">
-        <v>4104</v>
+        <v>4105</v>
       </c>
       <c r="F1018" s="0" t="s">
-        <v>4105</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="1019" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1019" s="0" t="s">
-        <v>4106</v>
+        <v>4107</v>
       </c>
       <c r="B1019" s="0" t="s">
         <v>658</v>
       </c>
       <c r="D1019" s="0" t="s">
-        <v>4107</v>
+        <v>4108</v>
       </c>
       <c r="E1019" s="0" t="s">
-        <v>4108</v>
+        <v>4109</v>
       </c>
       <c r="F1019" s="0" t="s">
-        <v>4109</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="1020" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1020" s="0" t="s">
-        <v>4110</v>
+        <v>4111</v>
       </c>
       <c r="B1020" s="0" t="s">
         <v>658</v>
       </c>
       <c r="D1020" s="0" t="s">
-        <v>4111</v>
+        <v>4112</v>
       </c>
       <c r="E1020" s="0" t="s">
-        <v>4112</v>
+        <v>4113</v>
       </c>
       <c r="F1020" s="0" t="s">
-        <v>4113</v>
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="1021" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1021" s="0" t="s">
+        <v>4115</v>
+      </c>
+      <c r="B1021" s="0" t="s">
+        <v>658</v>
+      </c>
+      <c r="D1021" s="0" t="s">
+        <v>4116</v>
+      </c>
+      <c r="E1021" s="0" t="s">
+        <v>4117</v>
+      </c>
+      <c r="F1021" s="0" t="s">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="1022" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1022" s="0" t="s">
+        <v>4119</v>
+      </c>
+      <c r="B1022" s="0" t="s">
+        <v>3616</v>
+      </c>
+      <c r="D1022" s="0" t="s">
+        <v>4120</v>
+      </c>
+      <c r="E1022" s="0" t="s">
+        <v>4120</v>
+      </c>
+      <c r="F1022" s="0" t="s">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="1023" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1023" s="0" t="s">
+        <v>4121</v>
+      </c>
+      <c r="B1023" s="0" t="s">
+        <v>3616</v>
+      </c>
+      <c r="D1023" s="0" t="s">
+        <v>4122</v>
+      </c>
+      <c r="E1023" s="0" t="s">
+        <v>4122</v>
+      </c>
+      <c r="F1023" s="0" t="s">
+        <v>4122</v>
       </c>
     </row>
   </sheetData>
